--- a/sdk/sdk_第二周_多人协作文献综述记录模板.xlsx
+++ b/sdk/sdk_第二周_多人协作文献综述记录模板.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="430">
   <si>
     <t>序号</t>
   </si>
@@ -651,7 +651,79 @@
     <t>从单个 RGB-D 人类视频教 humanoid 执行桌面操作，并用生成轨迹训练闭环策略。</t>
   </si>
   <si>
-    <t>humanoid manipulation 的遥操作示范成本高；单视频 imitation 往往难以把人类动作、物体位置和 humanoid 高 DoF 约束统一起来。</t>
+    <r>
+      <t xml:space="preserve">humanoid manipulation </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的遥操作示范成本高；单视频</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> imitation </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>往往难以把人类动作、物体位置和</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> humanoid </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>高</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> DoF </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>约束统一起来。</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">   用开放视觉模型识别任务物体并重建人体动作；进行 object-aware task-space warping 和 IK retargeting，将手臂和手指动作转成 humanoid 轨迹；筛选成功 rollout 训练 ACT 闭环策略。它先从视频里恢复人体运动和任务相关物体位置，形成 reference manipulation plan，再在测试环境里根据目标物体的新位置做 object-aware retargeting；视觉部分用 foundation models 自动找任务相关物体，减少人工标注或额外输入。论文还把 OKAMI 生成的成功 rollout 拿来训练闭环 visuomotor policy，并在真实 GR1 和 robosuite 任务中检查空间布局、视觉背景和新物体实例变化下的表现</t>
@@ -660,18 +732,1582 @@
     <t>OKAMI 的贡献是把单个 RGB-D 人类视频转成 humanoid 可执行的操作轨迹。。</t>
   </si>
   <si>
-    <t>OKAMI 用的是“单个人类视频示范 -&gt; 生成 humanoid 轨迹”的路线。真实机器人是 Fourier GR1 humanoid，双 6-DoF Inspire dexterous hands；感知用 Intel RealSense D435i RGB-D 相机，既录制人类示范，也提供测试时 RGB-D 观测。控制上，OKAMI 用 GPT-4V/大视觉模型解析视频，结合 SMPL-H/人体重建、object-aware task-space warping、IK 和 hand retargeting 生成机器人轨迹；机器人命令 40 Hz 计算，再插值到 400 Hz joint position controller。仿真部分用 robosuite 的 GR1FixedLowerBody；闭环策略实验用 ACT + DinoV2。
-数据不是遥操作 demonstrations，而是每个任务 1 个 RGB-D 人类视频示范；部分成功的 OKAMI rollouts 再被拿来训练 ACT。任务和数量如下：
-1. Plush-toy-in-basket：1 个 RGB-D 人类视频示范；真实机器人评估 12 trials，物体位置在相机视野/可达范围内随机。
-2. Sprinkle-salt：1 个 RGB-D 人类视频示范；真实机器人评估 12 trials；robosuite 仿真评估 50 rollouts/task/method；闭环 ACT 训练使用 50 条成功 OKAMI trajectories。
-3. Close-the-drawer：1 个 RGB-D 人类视频示范；真实机器人评估 12 trials；robosuite 仿真评估 50 rollouts/task/method。
-4. Close-the-laptop：1 个 RGB-D 人类视频示范；真实机器人评估 12 trials；另做 3 个不同 demonstrators 的单视频示范实验。
-5. Place-snacks-on-plate：1 个 RGB-D 人类视频示范；真实机器人评估 12 trials；另做 3 个不同 demonstrators 的单视频示范实验。
-6. Bagging：1 个 RGB-D 人类视频示范；真实机器人评估 12 trials；闭环 ACT 训练使用 100 条成功 OKAMI trajectories。
-泛化实验包括随机化真实任务物体位置，以及在 Place-snacks-on-plate、Plush-toy-in-basket、Sprinkle-salt 中更换 plate/snack bag/plush toy/bowl 等 unseen object instances。ACT 策略的训练轨迹数给得很清楚，但该策略实验单独的评估 rollout 数论文未报告具体数量。</t>
-  </si>
-  <si>
-    <t>task success；grasp failure/completion failure；真实任务 12 trials；仿真 50 rollouts；50/100 生成轨迹训练后的 policy success。</t>
+    <r>
+      <t xml:space="preserve">OKAMI </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>用的是</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单个人类视频示范</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>生成</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> humanoid </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>轨迹</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>”</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的路线。真实机器人是</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Fourier GR1 humanoid</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，双</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 6-DoF Inspire dexterous hands</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；感知用</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Intel RealSense D435i RGB-D </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>相机，既录制人类示范，也提供测试时</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> RGB-D </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>观测。控制上，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">OKAMI </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>用</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> GPT-4V/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>大视觉模型解析视频，结合</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> SMPL-H/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>人体重建、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>object-aware task-space warping</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">IK </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>和</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> hand retargeting </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>生成机器人轨迹；机器人命令</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 40 Hz </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>计算，再插值到</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 400 Hz joint position controller</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。仿真部分用</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> robosuite </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> GR1FixedLowerBody</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；闭环策略实验用</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> ACT + DinoV2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数据不是遥操作</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> demonstrations</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，而是每个任务</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 1 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> RGB-D </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>人类视频示范；部分成功的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> OKAMI rollouts </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>再被拿来训练</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> ACT</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。任务和数量如下：</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Plush-toy-in-basket</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> RGB-D </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>人类视频示范；真实机器人评估</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 12 trials</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，物体位置在相机视野</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>可达范围内随机。</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+2. Sprinkle-salt</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> RGB-D </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>人类视频示范；真实机器人评估</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 12 trials</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">robosuite </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>仿真评估</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 50 rollouts/task/method</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；闭环</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> ACT </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>训练使用</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 50 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>条成功</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> OKAMI trajectories</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+3. Close-the-drawer</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> RGB-D </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>人类视频示范；真实机器人评估</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 12 trials</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">robosuite </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>仿真评估</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 50 rollouts/task/method</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+4. Close-the-laptop</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> RGB-D </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>人类视频示范；真实机器人评估</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 12 trials</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；另做</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 3 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个不同</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> demonstrators </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的单视频示范实验。</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+5. Place-snacks-on-plate</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> RGB-D </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>人类视频示范；真实机器人评估</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 12 trials</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；另做</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 3 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个不同</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> demonstrators </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的单视频示范实验。</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+6. Bagging</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> RGB-D </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>人类视频示范；真实机器人评估</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 12 trials</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；闭环</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> ACT </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>训练使用</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 100 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>条成功</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> OKAMI trajectories</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>泛化实验包括随机化真实任务物体位置，以及在</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Place-snacks-on-plate</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Plush-toy-in-basket</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Sprinkle-salt </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中更换</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> plate/snack bag/plush toy/bowl </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>等</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> unseen object instances</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">ACT </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>策略的训练轨迹数给得很清楚，但该策略实验单独的评估</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> rollout </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数论文未报告具体数量。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>task success</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t>grasp failure/completion failure</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；真实任务</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 12 trials</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；仿真</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 50 rollouts</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">50/100 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>生成轨迹训练后的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> policy success</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
   </si>
   <si>
     <t>六个真实任务平均成功率 71.7%，明显优于 ORION；用 OKAMI rollout 训练闭环策略后平均约 79.2%，但仍依赖成功轨迹筛选。</t>
@@ -683,9 +2319,141 @@
     <t>论文不能直接使用普通 Internet RGB 视频，这严重限制了“single video imitation”的规模化想象。当前任务是 tabletop upper-body manipulation，没有 whole-body controller，也没有处理移动、平衡、避障和大范围环境交互。retargeting 对大幅物体形状变化不鲁棒，说明它更多是在相似物体和相似桌面布局上做几何迁移。它展示了从单个 RGB-D 示例启动策略学习的潜力，但还没有证明能处理开放世界 humanoid imitation。</t>
   </si>
   <si>
-    <t>1. 从 RGB-D 单视频扩展到普通 RGB 视频，这是利用互联网视频规模的关键。
-2. 提高 retargeting 对物体形状和布局变化的鲁棒性。
-3. 加入失败检测和轨迹筛选，避免错误 rollout 污染闭环策略。</t>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>从</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> RGB-D </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单视频扩展到普通</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> RGB </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>视频，这是利用互联网视频规模的关键。</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提高</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> retargeting </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>对物体形状和布局变化的鲁棒性。</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>加入失败检测和轨迹筛选，避免错误</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> rollout </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>污染闭环策略。</t>
+    </r>
   </si>
   <si>
     <t>与本地文献007 EgoMimic 同属人类视频学习路线；010 偏单示例几何 retargeting，007 偏人机数据共训。与本地文献008 iDP3 的关系是：010 可生成数据，008 可作为后续 3D policy。</t>
@@ -697,9 +2465,6 @@
     <t>待分配</t>
   </si>
   <si>
-    <t>数据采集系统</t>
-  </si>
-  <si>
     <t>高</t>
   </si>
   <si>
@@ -709,16 +2474,13 @@
     <t>Kenneth Shaw, Yulong Li, Jiahui Yang et al.</t>
   </si>
   <si>
-    <t>CoRL 2024 / arXiv</t>
+    <t xml:space="preserve">CoRL 2024 </t>
   </si>
   <si>
     <t>arXiv:2411.13677；https://bidex-teleop.github.io/</t>
   </si>
   <si>
     <t>双臂多指遥操作与模仿学习：用低成本、便携式 BiDex 系统采集复杂双手灵巧操作数据并训练闭环策略。</t>
-  </si>
-  <si>
-    <t>Bimanual Teleoperation；Dexterous Hands；Behavior Cloning；ACT</t>
   </si>
   <si>
     <t>高质量双臂多指机器人示范很难采集；VR 头显腕部跟踪抖动、手指跟踪不准，SteamVR 依赖外部 lighthouse，难以支持移动和复杂双手任务。</t>
@@ -756,28 +2518,16 @@
     <t>复杂双手灵巧操作的数据质量很大程度取决于遥操作接口本身；稳定、低延迟、可移动的双臂多指接口能直接提升示范效率和后续策略质量。</t>
   </si>
   <si>
-    <t>6 Sim-to-Real and Data Collection</t>
-  </si>
-  <si>
-    <t>需人工复核附录用户研究图中的精确曲线数值。</t>
-  </si>
-  <si>
     <t>DexHub and DART: Towards Internet Scale Robot Data Collection</t>
   </si>
   <si>
     <t>Younghyo Park, Jagdeep Singh Bhatia, Lars Ankile, Pulkit Agrawal</t>
   </si>
   <si>
-    <t>arXiv</t>
-  </si>
-  <si>
-    <t>arXiv:2411.02214；https://dexhub.ai/project</t>
+    <t>https://doi.org/10.48550/arXiv.2411.02214</t>
   </si>
   <si>
     <t>面向互联网规模机器人数据采集：用 AR+云端仿真进行 dexterous teleoperation，并用 DexHub 统一存储机器人数据。</t>
-  </si>
-  <si>
-    <t>Augmented Reality Teleoperation；Cloud Simulation；Robot Data Hub；Sim-to-Real Imitation Learning</t>
   </si>
   <si>
     <t>真实机器人数据采集受硬件、场景搭建、复位、远程视觉延迟和数据存储割裂限制，难以像互联网视觉/语言数据一样持续增长。</t>
@@ -815,25 +2565,16 @@
     <t>机器人数据规模化不只取决于遥操作硬件，还取决于场景复位、数据存储、仿真随机化和社区化共享基础设施。</t>
   </si>
   <si>
-    <t>需人工复核表 III 中各用户研究问卷分项的完整数值。</t>
-  </si>
-  <si>
-    <t>主动感知/遥操作</t>
-  </si>
-  <si>
     <t>Learning to Look Around: Enhancing Teleoperation and Learning with a Human-like Actuated Neck</t>
   </si>
   <si>
     <t>Bipasha Sen, Michelle Wang, Nandini Thakur, Aditya Agarwal, Pulkit Agrawal</t>
   </si>
   <si>
-    <t>arXiv:2411.00704</t>
+    <t>https://doi.org/10.48550/arXiv.2411.00704</t>
   </si>
   <si>
     <t>带 5-DOF 类人主动颈部的移动操作遥操作和模仿学习，关注动态视角、遮挡处理和全身任务。</t>
-  </si>
-  <si>
-    <t>Active Perception；Teleoperation；Imitation Learning；Actuated Neck；Whole-body Manipulation</t>
   </si>
   <si>
     <t>固定广角相机或静态机载视角在复杂家庭操作中难以处理遮挡、近身物体和高低位置变化；遥操作和策略学习都需要“看哪里”的自由度。</t>
@@ -871,30 +2612,21 @@
     <t>对 humanoid/mobile manipulation 来说，感知自由度不是附属模块，而会直接改变遥操作可行性和模仿学习的状态分布。</t>
   </si>
   <si>
-    <t>3 Learning-based Control</t>
-  </si>
-  <si>
-    <t>正文未报告七个遥操作任务的逐项定量结果，表中不据视频补写额外数字。</t>
-  </si>
-  <si>
-    <t>模仿学习</t>
-  </si>
-  <si>
     <t>Object-Centric Dexterous Manipulation from Human Motion Data</t>
   </si>
   <si>
     <t>Yuanpei Chen, Chen Wang, Yaodong Yang, C. Karen Liu</t>
   </si>
   <si>
-    <t>arXiv:2411.04005；https://cypypccpy.github.io/obj-dex.github.io/</t>
+    <t>arXiv</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.48550/arXiv.2411.04005</t>
   </si>
   <si>
     <t>从人类手-物 mocap 数据学习物体中心灵巧操作策略，并迁移到双臂 Shadow Hand 真实系统。</t>
   </si>
   <si>
-    <t>Object-centric Imitation；Hierarchical Policy；Dexterous RL；Human Motion Data；Sim-to-Real</t>
-  </si>
-  <si>
     <t>人手动作蕴含丰富操作技能，但直接把人手手指轨迹 retarget 到机器人手会受到 embodiment gap 影响；同时纯 RL 同时学习手臂和多指动作探索成本很高。</t>
   </si>
   <si>
@@ -910,10 +2642,410 @@
     <t>wrist trajectory translation/orientation error；completion rate；unseen trajectory/object generalization；real-world completion rate。</t>
   </si>
   <si>
-    <t>高层 planner 在 trained/unseen trajectory/unseen object 条件下均低于 MLP/RNN 的累计误差；单对象策略中 Ours 在 Box/Microwave/Laptop 等达到 100% 或接近 100%，传统 finger/fingertip mapping 多数低于 40%。泛化表中 Ours 在 Single Obj-Trained/Unseen Traj、Multi Obj-Trained/Unseen Obj 为 83.8%/57.1%/47.6%/36.4%。真实实验中 Box/Microwave/Laptop/Coffee/Mixer/Notebook 为 69.8%/100%/76.7%/74.8%/82.8%/64.3%，明显高于 mapping 和 vanilla RL。</t>
-  </si>
-  <si>
-    <t>相对 DexCap/OKAMI 中常见的直接 IK retargeting，014 不把人手手指轨迹直接当机器人动作，而是使用物体中心目标和人类腕部运动引导低层 RL，从而更正面地处理 embodiment gap。</t>
+    <r>
+      <t>高层</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> planner </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> trained/unseen trajectory/unseen object </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>条件下均低于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> MLP/RNN </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的累计误差；单对象策略中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Ours </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Box/Microwave/Laptop </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>等达到</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 100% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>或接近</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 100%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，传统</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> finger/fingertip mapping </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>多数低于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 40%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。泛化表中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Ours </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Single Obj-Trained/Unseen Traj</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Multi Obj-Trained/Unseen Obj </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 83.8%/57.1%/47.6%/36.4%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。真实实验中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Box/Microwave/Laptop/Coffee/Mixer/Notebook </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 69.8%/100%/76.7%/74.8%/82.8%/64.3%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，明显高于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> mapping </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>和</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> vanilla RL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>相对</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> DexCap/OKAMI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中常见的直接</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> IK retargeting</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">014 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不把人手手指轨迹直接当机器人动作，而是使用物体中心目标和人类腕部运动引导低层</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> RL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，从而更正面地处理</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> embodiment gap</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
   </si>
   <si>
     <t>小物体如 scissors、ketchup 表现较弱；没有使用 ARCTIC 中的触觉信息；真实初始位姿与目标轨迹差异过大时会失败；手遮挡会造成真实物体姿态估计错误；关节顺序需要预定义，跨类别泛化受 ARCTIC 对象数限制。</t>
@@ -930,31 +3062,80 @@
     <t>物体中心表征能把“模仿人手动作”转化为“达成物体状态变化”，是缓解人手到机器人手形态差异的一条重要路线。</t>
   </si>
   <si>
-    <t>4 Imitation Learning and Learning from Demonstration</t>
-  </si>
-  <si>
-    <t>小物体实验和附录中的额外 goal representation/time-indexed 实验可再精读。</t>
-  </si>
-  <si>
     <t>ARMADA: Augmented Reality for Robot Manipulation and Robot-Free Data Acquisition</t>
   </si>
   <si>
     <t>Nataliya Nechyporenko, Ryan Hoque, Christopher Webb, Mouli Sivapurapu, Jian Zhang</t>
   </si>
   <si>
-    <t>arXiv / Apple ML Research</t>
-  </si>
-  <si>
-    <t>arXiv:2412.10631；https://nataliya.dev/armada</t>
-  </si>
-  <si>
-    <t>用 Apple Vision Pro 中的实时虚拟机器人反馈收集不依赖实体机器人在场的操作示范，并直接回放到真实双臂机器人。</t>
-  </si>
-  <si>
-    <t>Augmented Reality；Robot-free Data Acquisition；Human Demonstration；Trajectory Replay</t>
-  </si>
-  <si>
-    <t>没有机器人硬件的人很难提供可用于机器人模仿学习的数据；裸手人类动作如果没有机器人 embodiment 反馈，常会超出机器人工作空间、速度或 IK 约束，导致不能直接回放。</t>
+    <t xml:space="preserve">arXiv </t>
+  </si>
+  <si>
+    <t>https://doi.org/10.48550/arXiv.2412.10631</t>
+  </si>
+  <si>
+    <r>
+      <t>用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Apple Vision Pro </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中的实时虚拟机器人反馈收集不依赖实体机器人在场的操作示范，并直接回放到真实双臂机器人。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>没有机器人硬件的人很难提供可用于机器人模仿学习的数据；裸手人类动作如果没有机器人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> embodiment </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>反馈，常会超出机器人工作空间、速度或</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> IK </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Serif CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>约束，导致不能直接回放。</t>
+    </r>
   </si>
   <si>
     <t>ARMADA 在 Vision Pro passthrough 中叠加虚拟机器人，让用户边做裸手动作边实时看到机器人如何执行，并可显示奇异、速度、工作空间等约束；系统记录机器人关节轨迹，再在真实 Interbotix 双臂硬件上直接回放。</t>
@@ -989,28 +3170,19 @@
     <t>AR 中的机器人反馈可以把普通人类动作变成更接近机器人可执行空间的数据，是降低机器人数据采集硬件门槛的重要方向。</t>
   </si>
   <si>
-    <t>未报告闭环策略训练结果；复杂接触/多指任务缺失。</t>
-  </si>
-  <si>
-    <t>人机交互/仿真数据</t>
-  </si>
-  <si>
     <t>MobileH2R: Learning Generalizable Human to Mobile Robot Handover Exclusively from Scalable and Diverse Synthetic Data</t>
   </si>
   <si>
     <t>Zifan Wang, Ziqing Chen, Junyu Chen et al.</t>
   </si>
   <si>
-    <t>CVPR 2025 / arXiv</t>
-  </si>
-  <si>
-    <t>arXiv:2501.04595；https://MobileH2R.github.io/</t>
+    <t xml:space="preserve">CVPR 2025 </t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2501.04595</t>
   </si>
   <si>
     <t>人到移动机器人递交 H2MR：只用大规模合成数据学习视觉闭环、底盘-机械臂协调的接物策略。</t>
-  </si>
-  <si>
-    <t>Synthetic Data；Human-Robot Handover；Mobile Manipulation；4D Imitation Learning；Sim-to-Real</t>
   </si>
   <si>
     <t>传统 H2R handover 多为固定基座或真实数据采集，移动机器人需要在大范围内理解全身人类动作并协调底盘和机械臂，真实训练既危险又难规模化。</t>
@@ -1048,9 +3220,6 @@
     <t>对于涉及人的移动操作，规模化学习需要同时解决数据多样性、示范安全性和视觉-动作可模仿性，而不只是堆叠轨迹数量。</t>
   </si>
   <si>
-    <t>作者列表已压缩为 et al.；真实实验补充细节可复核。</t>
-  </si>
-  <si>
     <t>研究阶段/主线</t>
   </si>
   <si>
@@ -1399,10 +3568,16 @@
     <t>2 Model-based Control</t>
   </si>
   <si>
+    <t>模仿学习</t>
+  </si>
+  <si>
     <t>Online RL</t>
   </si>
   <si>
     <t>方法改进</t>
+  </si>
+  <si>
+    <t>3 Learning-based Control</t>
   </si>
   <si>
     <t>低</t>
@@ -1484,7 +3659,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1506,6 +3681,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Carlito"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Carlito"/>
       <charset val="134"/>
     </font>
@@ -1539,6 +3720,21 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Noto Serif CJK SC"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -2009,153 +4205,153 @@
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="42" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="4">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="5">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="4">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="6">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2175,22 +4371,38 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2552,85 +4764,85 @@
   </cols>
   <sheetData>
     <row r="1" ht="28.8" customHeight="1" spans="1:27">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="O1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="P1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="Q1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="R1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="7" t="s">
+      <c r="S1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="7" t="s">
+      <c r="T1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="7" t="s">
+      <c r="U1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="7" t="s">
+      <c r="V1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="7" t="s">
+      <c r="W1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="7" t="s">
+      <c r="X1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="7" t="s">
+      <c r="Y1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="7" t="s">
+      <c r="Z1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="7" t="s">
+      <c r="AA1" s="8" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2648,7 +4860,7 @@
       <c r="D2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="10" t="s">
         <v>30</v>
       </c>
       <c r="F2" s="3" t="s">
@@ -2663,7 +4875,7 @@
       <c r="I2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K2" s="4" t="s">
@@ -2723,13 +4935,13 @@
       <c r="D3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="10" t="s">
         <v>47</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="12" t="s">
         <v>49</v>
       </c>
       <c r="H3" s="3">
@@ -2738,7 +4950,7 @@
       <c r="I3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="13" t="s">
         <v>51</v>
       </c>
       <c r="K3" s="4" t="s">
@@ -2811,7 +5023,7 @@
       <c r="I4" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="13" t="s">
         <v>67</v>
       </c>
       <c r="K4" s="4" t="s">
@@ -2883,7 +5095,7 @@
       <c r="I5" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="13" t="s">
         <v>84</v>
       </c>
       <c r="K5" s="4" t="s">
@@ -2955,7 +5167,7 @@
       <c r="I6" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="11" t="s">
         <v>101</v>
       </c>
       <c r="K6" s="4" t="s">
@@ -3012,7 +5224,7 @@
       <c r="D7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F7" s="3" t="s">
@@ -3027,7 +5239,7 @@
       <c r="I7" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J7" s="12" t="s">
+      <c r="J7" s="13" t="s">
         <v>116</v>
       </c>
       <c r="K7" s="4" t="s">
@@ -3084,7 +5296,7 @@
       <c r="D8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="10" t="s">
         <v>129</v>
       </c>
       <c r="F8" s="3" t="s">
@@ -3099,7 +5311,7 @@
       <c r="I8" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="J8" s="12" t="s">
+      <c r="J8" s="13" t="s">
         <v>133</v>
       </c>
       <c r="K8" s="4" t="s">
@@ -3109,7 +5321,7 @@
       <c r="M8" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="N8" s="9" t="str">
+      <c r="N8" s="10" t="str">
         <f>_xlfn.DISPIMG("ID_CC0406E2CC454FC785296EC375B39D36",1)</f>
         <v>=DISPIMG("ID_CC0406E2CC454FC785296EC375B39D36",1)</v>
       </c>
@@ -3157,7 +5369,7 @@
       <c r="D9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="10" t="s">
         <v>145</v>
       </c>
       <c r="F9" s="3" t="s">
@@ -3172,7 +5384,7 @@
       <c r="I9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="J9" s="12" t="s">
+      <c r="J9" s="13" t="s">
         <v>148</v>
       </c>
       <c r="K9" s="4" t="s">
@@ -3244,7 +5456,7 @@
       <c r="I10" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="J10" s="13" t="s">
         <v>164</v>
       </c>
       <c r="K10" s="4" t="s">
@@ -3287,75 +5499,75 @@
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
     </row>
-    <row r="11" ht="291" customHeight="1" spans="1:27">
-      <c r="A11" s="3">
+    <row r="11" s="7" customFormat="1" ht="291" customHeight="1" spans="1:27">
+      <c r="A11" s="14">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3" t="s">
+      <c r="B11" s="14"/>
+      <c r="C11" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
+      <c r="E11" s="14"/>
+      <c r="F11" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="14">
         <v>2024</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="J11" s="12" t="s">
+      <c r="J11" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="L11" s="3"/>
-      <c r="M11" s="5" t="s">
+      <c r="L11" s="14"/>
+      <c r="M11" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="N11" s="4" t="s">
+      <c r="N11" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="O11" s="4" t="s">
+      <c r="O11" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="P11" s="5" t="s">
+      <c r="P11" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="Q11" s="5" t="s">
+      <c r="Q11" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="R11" s="4" t="s">
+      <c r="R11" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="S11" s="4" t="s">
+      <c r="S11" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="T11" s="4" t="s">
+      <c r="T11" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="U11" s="5" t="s">
+      <c r="U11" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="V11" s="4" t="s">
+      <c r="V11" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="W11" s="4" t="s">
+      <c r="W11" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
-      <c r="AA11" s="3"/>
+      <c r="X11" s="14"/>
+      <c r="Y11" s="14"/>
+      <c r="Z11" s="14"/>
+      <c r="AA11" s="14"/>
     </row>
     <row r="12" ht="234" spans="1:27">
       <c r="A12" s="3">
@@ -3368,78 +5580,68 @@
       <c r="C12" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>194</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>195</v>
       </c>
       <c r="H12" s="3">
         <v>2024</v>
       </c>
       <c r="I12" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="K12" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="L12" s="3"/>
+      <c r="M12" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="L12" s="3" t="s">
+      <c r="N12" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="M12" s="3" t="s">
+      <c r="O12" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="N12" s="3" t="s">
+      <c r="P12" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="O12" s="3" t="s">
+      <c r="Q12" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="P12" s="3" t="s">
+      <c r="R12" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="Q12" s="3" t="s">
+      <c r="S12" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="R12" s="3" t="s">
+      <c r="T12" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="S12" s="3" t="s">
+      <c r="U12" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="T12" s="3" t="s">
+      <c r="V12" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="U12" s="3" t="s">
+      <c r="W12" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="W12" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="X12" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA12" s="3" t="s">
-        <v>212</v>
-      </c>
+      <c r="X12" s="3"/>
+      <c r="Y12" s="3"/>
+      <c r="Z12" s="3"/>
+      <c r="AA12" s="4"/>
     </row>
     <row r="13" ht="216" spans="1:27">
       <c r="A13" s="3">
@@ -3452,78 +5654,68 @@
       <c r="C13" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="F13" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="H13" s="3">
         <v>2024</v>
       </c>
       <c r="I13" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="J13" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="L13" s="5"/>
+      <c r="M13" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="O13" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="P13" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="K13" s="3" t="s">
+      <c r="Q13" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="L13" s="3" t="s">
+      <c r="R13" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="M13" s="3" t="s">
+      <c r="S13" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="N13" s="3" t="s">
+      <c r="T13" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="O13" s="3" t="s">
+      <c r="U13" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="P13" s="3" t="s">
+      <c r="V13" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="Q13" s="3" t="s">
+      <c r="W13" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="R13" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="S13" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="T13" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="U13" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="V13" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="W13" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="X13" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA13" s="3" t="s">
-        <v>230</v>
-      </c>
+      <c r="X13" s="3"/>
+      <c r="Y13" s="3"/>
+      <c r="Z13" s="3"/>
+      <c r="AA13" s="3"/>
     </row>
     <row r="14" ht="180" spans="1:27">
       <c r="A14" s="3">
@@ -3536,78 +5728,68 @@
       <c r="C14" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>231</v>
+      <c r="D14" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="H14" s="3">
         <v>2024</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="J14" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="J14" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="S14" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="U14" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="V14" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="W14" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>249</v>
-      </c>
+      <c r="X14" s="3"/>
+      <c r="Y14" s="3"/>
+      <c r="Z14" s="3"/>
+      <c r="AA14" s="3"/>
     </row>
     <row r="15" ht="264" spans="1:27">
       <c r="A15" s="3">
@@ -3620,78 +5802,68 @@
       <c r="C15" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>250</v>
+      <c r="D15" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="H15" s="3">
         <v>2024</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="J15" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="J15" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="R15" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="S15" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="V15" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="W15" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="R15" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="U15" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="V15" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="W15" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="X15" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="Y15" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z15" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA15" s="3" t="s">
-        <v>268</v>
-      </c>
+      <c r="X15" s="3"/>
+      <c r="Y15" s="3"/>
+      <c r="Z15" s="3"/>
+      <c r="AA15" s="3"/>
     </row>
     <row r="16" ht="216" spans="1:27">
       <c r="A16" s="3">
@@ -3704,78 +5876,68 @@
       <c r="C16" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="F16" s="3" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="H16" s="3">
         <v>2024</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>275</v>
+        <v>257</v>
+      </c>
+      <c r="J16" s="18" t="s">
+        <v>258</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="L16" s="3"/>
+      <c r="M16" s="4" t="s">
+        <v>260</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="W16" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="X16" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z16" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA16" s="3" t="s">
-        <v>286</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
     </row>
     <row r="17" ht="198" spans="1:27">
       <c r="A17" s="3">
@@ -3788,78 +5950,68 @@
       <c r="C17" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>287</v>
+      <c r="D17" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="H17" s="3">
         <v>2025</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>291</v>
+        <v>273</v>
+      </c>
+      <c r="J17" s="18" t="s">
+        <v>274</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>293</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="L17" s="3"/>
       <c r="M17" s="3" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="V17" s="3" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="W17" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="X17" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y17" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z17" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA17" s="3" t="s">
-        <v>305</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="X17" s="3"/>
+      <c r="Y17" s="3"/>
+      <c r="Z17" s="3"/>
+      <c r="AA17" s="3"/>
     </row>
     <row r="18" spans="1:27">
       <c r="A18" s="3"/>
@@ -6562,6 +8714,11 @@
     <hyperlink ref="J9" r:id="rId9" display="https://doi.org/10.48550/arXiv.2410.10803" tooltip="https://doi.org/10.48550/arXiv.2410.10803"/>
     <hyperlink ref="J10" r:id="rId10" display="https://doi.org/10.48550/arXiv.2410.18964" tooltip="https://doi.org/10.48550/arXiv.2410.18964"/>
     <hyperlink ref="J11" r:id="rId11" display="https://doi.org/10.48550/arXiv.2410.11792"/>
+    <hyperlink ref="J13" r:id="rId12" display="https://doi.org/10.48550/arXiv.2411.02214"/>
+    <hyperlink ref="J14" r:id="rId13" display="https://doi.org/10.48550/arXiv.2411.00704"/>
+    <hyperlink ref="J16" r:id="rId14" display="https://doi.org/10.48550/arXiv.2412.10631"/>
+    <hyperlink ref="J15" r:id="rId15" display="https://doi.org/10.48550/arXiv.2411.04005"/>
+    <hyperlink ref="J17" r:id="rId16" display="https://arxiv.org/abs/2501.04595"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -6587,210 +8744,210 @@
   <sheetData>
     <row r="1" ht="25.65" customHeight="1" spans="1:8">
       <c r="A1" s="6" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>307</v>
+        <v>288</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>309</v>
+        <v>290</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>313</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" ht="36" customHeight="1" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>316</v>
+        <v>297</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>319</v>
+        <v>300</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>321</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>322</v>
+        <v>303</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>325</v>
+        <v>306</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>326</v>
+        <v>307</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>329</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>331</v>
+        <v>312</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>336</v>
+        <v>317</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:8">
       <c r="A5" s="3" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>340</v>
+        <v>321</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>341</v>
+        <v>322</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>342</v>
+        <v>323</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>343</v>
+        <v>324</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>344</v>
+        <v>325</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>345</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1" spans="1:8">
       <c r="A6" s="3" t="s">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>350</v>
+        <v>331</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>351</v>
+        <v>332</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>352</v>
+        <v>333</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>353</v>
+        <v>334</v>
       </c>
     </row>
     <row r="7" ht="33" customHeight="1" spans="1:8">
       <c r="A7" s="3" t="s">
-        <v>354</v>
+        <v>335</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>356</v>
+        <v>337</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>357</v>
+        <v>338</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>358</v>
+        <v>339</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>361</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8" ht="54" customHeight="1" spans="1:8">
       <c r="A8" s="3" t="s">
-        <v>362</v>
+        <v>343</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>363</v>
+        <v>344</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>364</v>
+        <v>345</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>367</v>
+        <v>348</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>368</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -6946,16 +9103,16 @@
   <sheetData>
     <row r="1" ht="25.65" customHeight="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:4">
@@ -6963,13 +9120,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>373</v>
+        <v>354</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>374</v>
+        <v>355</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:4">
@@ -6977,13 +9134,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>376</v>
+        <v>357</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>377</v>
+        <v>358</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>378</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:4">
@@ -6991,13 +9148,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>379</v>
+        <v>360</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:4">
@@ -7005,13 +9162,13 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>383</v>
+        <v>364</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4">
@@ -7019,13 +9176,13 @@
         <v>9</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>384</v>
+        <v>365</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>385</v>
+        <v>366</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:4">
@@ -7033,13 +9190,13 @@
         <v>12</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>387</v>
+        <v>368</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>388</v>
+        <v>369</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>389</v>
+        <v>370</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:4">
@@ -7047,13 +9204,13 @@
         <v>13</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>390</v>
+        <v>371</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>391</v>
+        <v>372</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>392</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:4">
@@ -7061,13 +9218,13 @@
         <v>14</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>393</v>
+        <v>374</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>394</v>
+        <v>375</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>395</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:4">
@@ -7075,13 +9232,13 @@
         <v>18</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>396</v>
+        <v>377</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>398</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:4">
@@ -7089,13 +9246,13 @@
         <v>19</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>400</v>
+        <v>381</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>401</v>
+        <v>382</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:4">
@@ -7103,13 +9260,13 @@
         <v>20</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>402</v>
+        <v>383</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>403</v>
+        <v>384</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>404</v>
+        <v>385</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:4">
@@ -7117,13 +9274,13 @@
         <v>21</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>405</v>
+        <v>386</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>406</v>
+        <v>387</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>407</v>
+        <v>388</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:4">
@@ -7131,13 +9288,13 @@
         <v>22</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>408</v>
+        <v>389</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>409</v>
+        <v>390</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>410</v>
+        <v>391</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -7204,7 +9361,7 @@
         <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>411</v>
+        <v>392</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>23</v>
@@ -7215,39 +9372,39 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
       <c r="B2" t="s">
-        <v>413</v>
+        <v>394</v>
       </c>
       <c r="C2" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
       <c r="D2" t="s">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="E2" t="s">
-        <v>416</v>
+        <v>397</v>
       </c>
       <c r="F2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="B3" t="s">
-        <v>418</v>
+        <v>399</v>
       </c>
       <c r="C3" t="s">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="D3" t="s">
-        <v>420</v>
+        <v>401</v>
       </c>
       <c r="E3" t="s">
-        <v>421</v>
+        <v>402</v>
       </c>
       <c r="F3" t="s">
         <v>97</v>
@@ -7258,118 +9415,118 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>250</v>
+        <v>403</v>
       </c>
       <c r="C4" t="s">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="D4" t="s">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="E4" t="s">
-        <v>248</v>
+        <v>406</v>
       </c>
       <c r="F4" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="B5" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="C5" t="s">
-        <v>426</v>
+        <v>409</v>
       </c>
       <c r="D5" t="s">
-        <v>427</v>
+        <v>410</v>
       </c>
       <c r="E5" t="s">
-        <v>428</v>
+        <v>411</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>429</v>
+        <v>412</v>
       </c>
       <c r="B6" t="s">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="C6" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="D6" t="s">
-        <v>431</v>
+        <v>414</v>
       </c>
       <c r="E6" t="s">
-        <v>432</v>
+        <v>415</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="B7" t="s">
-        <v>354</v>
+        <v>335</v>
       </c>
       <c r="C7" t="s">
-        <v>433</v>
+        <v>416</v>
       </c>
       <c r="D7" t="s">
-        <v>434</v>
+        <v>417</v>
       </c>
       <c r="E7" t="s">
-        <v>435</v>
+        <v>418</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="B8" t="s">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="C8" t="s">
-        <v>344</v>
+        <v>325</v>
       </c>
       <c r="D8" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="E8" t="s">
-        <v>437</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="B9" t="s">
-        <v>438</v>
+        <v>421</v>
       </c>
       <c r="C9" t="s">
-        <v>439</v>
+        <v>422</v>
       </c>
       <c r="D9" t="s">
-        <v>440</v>
+        <v>423</v>
       </c>
       <c r="E9" t="s">
-        <v>441</v>
+        <v>424</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="C10" t="s">
-        <v>442</v>
+        <v>425</v>
       </c>
       <c r="D10" t="s">
-        <v>443</v>
+        <v>426</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="C11" t="s">
-        <v>444</v>
+        <v>427</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="C12" t="s">
-        <v>445</v>
+        <v>428</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="C13" t="s">
-        <v>446</v>
+        <v>429</v>
       </c>
     </row>
   </sheetData>
